--- a/data/trans_dic/P25A$preocupacion-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P25A$preocupacion-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, la preocupación por sus efectos nocivos</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, la preocupación por sus efectos nocivos (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,99; 20,69</t>
+          <t>3,94; 20,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,38; 21,66</t>
+          <t>6,56; 22,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,07; 18,95</t>
+          <t>3,92; 17,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,24</t>
+          <t>0,0; 35,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,77; 40,39</t>
+          <t>9,86; 41,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,8; 17,85</t>
+          <t>1,93; 18,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,62; 18,96</t>
+          <t>4,84; 20,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,3; 24,66</t>
+          <t>9,05; 23,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,49; 14,76</t>
+          <t>4,62; 14,72</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,85; 10,66</t>
+          <t>2,63; 11,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,33; 10,1</t>
+          <t>1,71; 10,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,02; 29,59</t>
+          <t>9,55; 28,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 7,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,71; 13,25</t>
+          <t>1,7; 13,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,3; 25,75</t>
+          <t>3,28; 28,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,11; 8,99</t>
+          <t>1,51; 8,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,26; 8,93</t>
+          <t>2,32; 8,8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,95; 23,59</t>
+          <t>8,44; 23,45</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,97; 19,44</t>
+          <t>2,96; 18,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,73</t>
+          <t>0,0; 6,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,32; 40,04</t>
+          <t>17,39; 39,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,42</t>
+          <t>0,0; 25,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,51; 45,16</t>
+          <t>13,39; 47,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,42; 16,06</t>
+          <t>2,37; 17,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 8,58</t>
+          <t>0,8; 9,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,68; 37,04</t>
+          <t>18,92; 37,7</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,63; 14,77</t>
+          <t>2,65; 15,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,92; 16,14</t>
+          <t>2,91; 17,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,35; 17,41</t>
+          <t>4,44; 19,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,65; 27,25</t>
+          <t>2,62; 27,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,93; 16,43</t>
+          <t>1,92; 16,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,09; 22,72</t>
+          <t>2,06; 22,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,89; 15,98</t>
+          <t>4,3; 15,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,26; 13,43</t>
+          <t>3,23; 13,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,0; 15,86</t>
+          <t>4,6; 16,28</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 4,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,07; 22,12</t>
+          <t>4,19; 23,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,33</t>
+          <t>0,0; 16,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 6,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,76</t>
+          <t>0,0; 22,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,23; 18,63</t>
+          <t>4,09; 17,52</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,65</t>
+          <t>0,0; 10,71</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,47; 23,67</t>
+          <t>5,81; 24,68</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,4; 13,46</t>
+          <t>1,28; 12,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,75; 16,87</t>
+          <t>1,7; 14,23</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11,09; 50,83</t>
+          <t>11,09; 51,39</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,92</t>
+          <t>0,0; 20,8</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,81</t>
+          <t>0,0; 33,82</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,65; 27,41</t>
+          <t>8,79; 27,1</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,92; 11,43</t>
+          <t>1,98; 11,58</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,7; 16,91</t>
+          <t>2,7; 16,32</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,96; 20,69</t>
+          <t>6,3; 20,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,42; 13,97</t>
+          <t>4,57; 14,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,09; 22,84</t>
+          <t>8,19; 22,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,18</t>
+          <t>0,0; 23,02</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,27; 12,98</t>
+          <t>2,22; 13,48</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,67; 16,37</t>
+          <t>3,78; 17,27</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,64; 18,41</t>
+          <t>5,95; 17,38</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,76; 11,76</t>
+          <t>4,26; 11,21</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,95; 18,34</t>
+          <t>7,89; 17,74</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,07; 9,33</t>
+          <t>2,12; 9,45</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,54; 17,68</t>
+          <t>6,26; 17,57</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,83; 10,8</t>
+          <t>1,82; 10,32</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,19; 17,91</t>
+          <t>3,28; 17,32</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,87; 16,41</t>
+          <t>2,94; 16,8</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0; 3,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,25; 9,78</t>
+          <t>3,63; 10,26</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>6,26; 15,67</t>
+          <t>6,37; 14,75</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,13; 6,79</t>
+          <t>1,17; 6,67</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,79; 9,94</t>
+          <t>5,66; 10,13</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,0; 9,94</t>
+          <t>5,93; 9,9</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9,35; 14,89</t>
+          <t>9,63; 14,93</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,27; 12,65</t>
+          <t>4,89; 12,15</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,53; 11,3</t>
+          <t>5,37; 11,19</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,52; 11,36</t>
+          <t>5,47; 11,47</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,07; 9,87</t>
+          <t>6,03; 9,92</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6,36; 9,77</t>
+          <t>6,35; 9,75</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8,84; 12,86</t>
+          <t>8,78; 12,93</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, la preocupación por sus efectos nocivos</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, la preocupación por sus efectos nocivos (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1852; 9611</t>
+          <t>1832; 9500</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5171; 17568</t>
+          <t>5324; 18281</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3217; 14966</t>
+          <t>3097; 13425</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 7074</t>
+          <t>0; 7029</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3513; 16168</t>
+          <t>3949; 16594</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>937; 9278</t>
+          <t>1004; 9628</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3071; 12613</t>
+          <t>3221; 13703</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11264; 29871</t>
+          <t>10966; 28614</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5874; 19326</t>
+          <t>6053; 19281</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2110; 12134</t>
+          <t>2996; 12784</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2820; 12212</t>
+          <t>2064; 12293</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6523; 21403</t>
+          <t>6907; 20367</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 1824</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1020; 7924</t>
+          <t>1020; 8169</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>968; 7543</t>
+          <t>961; 8350</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2953; 12561</t>
+          <t>2114; 12455</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4084; 16134</t>
+          <t>4195; 15910</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9097; 23972</t>
+          <t>8579; 23828</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1895; 12392</t>
+          <t>1888; 11896</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4712</t>
+          <t>0; 5426</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10737; 24828</t>
+          <t>10785; 24570</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 1795</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 8006</t>
+          <t>0; 8276</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3729; 12468</t>
+          <t>3696; 13080</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1884; 12526</t>
+          <t>1850; 13658</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>917; 9869</t>
+          <t>923; 11453</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>16738; 33194</t>
+          <t>16959; 33785</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1992; 11211</t>
+          <t>2015; 11813</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3080; 17013</t>
+          <t>3070; 17939</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3784; 15159</t>
+          <t>3863; 16756</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>999; 10267</t>
+          <t>988; 10203</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>897; 7637</t>
+          <t>892; 7492</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>933; 10145</t>
+          <t>918; 9837</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5555; 18146</t>
+          <t>4887; 17318</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4946; 20405</t>
+          <t>4905; 19949</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6590; 20899</t>
+          <t>6063; 21452</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1916</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2054; 11151</t>
+          <t>2115; 12080</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 6132</t>
+          <t>0; 5174</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 1975</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 6381</t>
+          <t>0; 6059</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 1800</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 1975</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3271; 14397</t>
+          <t>3162; 13542</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 4222</t>
+          <t>0; 5227</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2892; 12516</t>
+          <t>3072; 13051</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1998; 11187</t>
+          <t>1063; 10124</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>776; 7484</t>
+          <t>753; 6313</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2087; 9563</t>
+          <t>2086; 9668</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 4788</t>
+          <t>0; 4544</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 5680</t>
+          <t>0; 5683</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6919; 19648</t>
+          <t>6302; 19425</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2012; 11996</t>
+          <t>2074; 12157</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1650; 10342</t>
+          <t>1653; 9983</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>6410; 19070</t>
+          <t>5808; 18751</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>7192; 22710</t>
+          <t>7427; 23156</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11541; 28985</t>
+          <t>10397; 28633</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 7948</t>
+          <t>0; 7568</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2083; 11919</t>
+          <t>2037; 12379</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3096; 13824</t>
+          <t>3195; 14585</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8304; 23021</t>
+          <t>7444; 21725</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>12111; 29918</t>
+          <t>10847; 28511</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>16794; 38771</t>
+          <t>16676; 37500</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2874; 12928</t>
+          <t>2942; 13088</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>8519; 23027</t>
+          <t>8156; 22882</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1873; 11025</t>
+          <t>1860; 10534</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2302; 12930</t>
+          <t>2366; 12503</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1919; 10984</t>
+          <t>1966; 11242</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 2185</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>6853; 20607</t>
+          <t>7638; 21610</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>12341; 30892</t>
+          <t>12557; 29085</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1870; 11276</t>
+          <t>1949; 11069</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>36167; 62083</t>
+          <t>35340; 63240</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>48967; 81135</t>
+          <t>48425; 80815</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>56644; 90187</t>
+          <t>58291; 90426</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>13204; 31723</t>
+          <t>12250; 30475</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>21379; 43687</t>
+          <t>20743; 43260</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18524; 38153</t>
+          <t>18371; 38529</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>53133; 86402</t>
+          <t>52820; 86850</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>76504; 117461</t>
+          <t>76378; 117202</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>83249; 121094</t>
+          <t>82691; 121724</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25A$preocupacion-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P25A$preocupacion-Provincia-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,94; 20,45</t>
+          <t>3,98; 20,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,56; 22,54</t>
+          <t>5,8; 21,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,92; 17,0</t>
+          <t>4,21; 18,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,02</t>
+          <t>0,0; 34,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,86; 41,45</t>
+          <t>10,52; 42,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,93; 18,52</t>
+          <t>1,88; 16,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,84; 20,6</t>
+          <t>4,8; 19,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,05; 23,62</t>
+          <t>9,6; 25,27</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,62; 14,72</t>
+          <t>4,85; 14,69</t>
         </is>
       </c>
     </row>
@@ -788,17 +788,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,63; 11,23</t>
+          <t>1,85; 11,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,71; 10,16</t>
+          <t>1,77; 10,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,55; 28,16</t>
+          <t>9,43; 29,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -808,27 +808,27 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,7; 13,66</t>
+          <t>1,71; 14,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,28; 28,51</t>
+          <t>3,33; 27,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,51; 8,92</t>
+          <t>2,02; 9,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,32; 8,8</t>
+          <t>2,25; 9,01</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,44; 23,45</t>
+          <t>8,49; 22,98</t>
         </is>
       </c>
     </row>
@@ -898,17 +898,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,96; 18,66</t>
+          <t>2,94; 20,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,59</t>
+          <t>0,0; 4,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,39; 39,63</t>
+          <t>17,43; 39,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -918,27 +918,27 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,25</t>
+          <t>0,0; 29,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,39; 47,38</t>
+          <t>10,6; 45,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,37; 17,52</t>
+          <t>2,38; 17,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 9,95</t>
+          <t>0,8; 9,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,92; 37,7</t>
+          <t>17,96; 37,46</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,65; 15,57</t>
+          <t>3,6; 15,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,91; 17,01</t>
+          <t>2,95; 15,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,44; 19,24</t>
+          <t>4,52; 18,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,62; 27,08</t>
+          <t>4,98; 28,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,92; 16,11</t>
+          <t>1,93; 16,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,06; 22,02</t>
+          <t>2,06; 21,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,3; 15,25</t>
+          <t>4,37; 15,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,23; 13,13</t>
+          <t>3,17; 13,06</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,6; 16,28</t>
+          <t>4,96; 15,75</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,19; 23,96</t>
+          <t>4,08; 22,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,31</t>
+          <t>0,0; 13,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,56</t>
+          <t>0,0; 23,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1153,12 +1153,12 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,09; 17,52</t>
+          <t>4,2; 18,35</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,71</t>
+          <t>0,0; 10,42</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,81; 24,68</t>
+          <t>5,78; 24,97</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,28; 12,18</t>
+          <t>2,29; 13,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,7; 14,23</t>
+          <t>1,76; 16,44</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11,09; 51,39</t>
+          <t>10,95; 50,58</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,8</t>
+          <t>0,0; 20,62</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,82</t>
+          <t>0,0; 33,67</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,79; 27,1</t>
+          <t>9,87; 27,4</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,98; 11,58</t>
+          <t>1,93; 11,15</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,7; 16,32</t>
+          <t>2,78; 16,27</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,3; 20,35</t>
+          <t>6,66; 20,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,57; 14,25</t>
+          <t>5,02; 15,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,19; 22,56</t>
+          <t>8,71; 22,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,02</t>
+          <t>0,0; 24,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,22; 13,48</t>
+          <t>2,3; 12,55</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,78; 17,27</t>
+          <t>3,92; 16,61</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,95; 17,38</t>
+          <t>6,45; 18,29</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,26; 11,21</t>
+          <t>4,55; 11,66</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,89; 17,74</t>
+          <t>7,88; 17,8</t>
         </is>
       </c>
     </row>
@@ -1448,27 +1448,27 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,12; 9,45</t>
+          <t>2,13; 9,48</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,26; 17,57</t>
+          <t>6,27; 17,72</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,82; 10,32</t>
+          <t>1,74; 10,37</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,28; 17,32</t>
+          <t>3,41; 17,86</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,94; 16,8</t>
+          <t>2,94; 16,87</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1478,17 +1478,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,63; 10,26</t>
+          <t>3,49; 9,77</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>6,37; 14,75</t>
+          <t>6,13; 14,72</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,17; 6,67</t>
+          <t>1,1; 7,02</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,66; 10,13</t>
+          <t>5,79; 10,12</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5,93; 9,9</t>
+          <t>5,88; 9,88</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9,63; 14,93</t>
+          <t>9,32; 14,82</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,89; 12,15</t>
+          <t>5,27; 12,7</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,37; 11,19</t>
+          <t>5,51; 11,74</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,47; 11,47</t>
+          <t>5,61; 11,82</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,03; 9,92</t>
+          <t>6,11; 9,75</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6,35; 9,75</t>
+          <t>6,39; 9,65</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8,78; 12,93</t>
+          <t>8,66; 12,71</t>
         </is>
       </c>
     </row>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1832; 9500</t>
+          <t>1851; 9667</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5324; 18281</t>
+          <t>4701; 17726</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3097; 13425</t>
+          <t>3324; 14409</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 7029</t>
+          <t>0; 6827</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3949; 16594</t>
+          <t>4211; 16937</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1004; 9628</t>
+          <t>979; 8768</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3221; 13703</t>
+          <t>3195; 12662</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10966; 28614</t>
+          <t>11627; 30608</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6053; 19281</t>
+          <t>6352; 19231</t>
         </is>
       </c>
     </row>
@@ -2024,17 +2024,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2996; 12784</t>
+          <t>2111; 12626</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2064; 12293</t>
+          <t>2143; 12120</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6907; 20367</t>
+          <t>6822; 21132</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2044,27 +2044,27 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1020; 8169</t>
+          <t>1022; 8552</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>961; 8350</t>
+          <t>974; 7948</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2114; 12455</t>
+          <t>2818; 13360</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4195; 15910</t>
+          <t>4060; 16284</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8579; 23828</t>
+          <t>8630; 23352</t>
         </is>
       </c>
     </row>
@@ -2187,17 +2187,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1888; 11896</t>
+          <t>1875; 12900</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5426</t>
+          <t>0; 3766</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10785; 24570</t>
+          <t>10809; 24381</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -2207,27 +2207,27 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 8276</t>
+          <t>0; 9608</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3696; 13080</t>
+          <t>2928; 12574</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1850; 13658</t>
+          <t>1854; 13609</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>923; 11453</t>
+          <t>926; 10888</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>16959; 33785</t>
+          <t>16099; 33565</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2015; 11813</t>
+          <t>2730; 11707</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3070; 17939</t>
+          <t>3113; 16427</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3863; 16756</t>
+          <t>3940; 16075</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>988; 10203</t>
+          <t>1877; 10558</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>892; 7492</t>
+          <t>899; 7771</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>918; 9837</t>
+          <t>920; 9676</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4887; 17318</t>
+          <t>4963; 17492</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4905; 19949</t>
+          <t>4817; 19849</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6063; 21452</t>
+          <t>6534; 20752</t>
         </is>
       </c>
     </row>
@@ -2518,12 +2518,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2115; 12080</t>
+          <t>2058; 11362</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 5174</t>
+          <t>0; 4428</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 6059</t>
+          <t>0; 6209</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2548,12 +2548,12 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3162; 13542</t>
+          <t>3243; 14176</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 5227</t>
+          <t>0; 5084</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3072; 13051</t>
+          <t>3057; 13204</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1063; 10124</t>
+          <t>1900; 10879</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>753; 6313</t>
+          <t>783; 7296</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2086; 9668</t>
+          <t>2059; 9514</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 4544</t>
+          <t>0; 4506</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 5683</t>
+          <t>0; 5657</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6302; 19425</t>
+          <t>7075; 19639</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2074; 12157</t>
+          <t>2026; 11699</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1653; 9983</t>
+          <t>1701; 9953</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5808; 18751</t>
+          <t>6140; 19205</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>7427; 23156</t>
+          <t>8161; 24771</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10397; 28633</t>
+          <t>11052; 28407</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 7568</t>
+          <t>0; 7937</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2037; 12379</t>
+          <t>2109; 11522</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3195; 14585</t>
+          <t>3314; 14023</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7444; 21725</t>
+          <t>8067; 22867</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>10847; 28511</t>
+          <t>11563; 29661</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>16676; 37500</t>
+          <t>16652; 37615</t>
         </is>
       </c>
     </row>
@@ -3002,27 +3002,27 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2942; 13088</t>
+          <t>2951; 13130</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>8156; 22882</t>
+          <t>8168; 23073</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1860; 10534</t>
+          <t>1775; 10592</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2366; 12503</t>
+          <t>2459; 12891</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1966; 11242</t>
+          <t>1967; 11293</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -3032,17 +3032,17 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>7638; 21610</t>
+          <t>7347; 20575</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>12557; 29085</t>
+          <t>12084; 29020</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1949; 11069</t>
+          <t>1824; 11663</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>35340; 63240</t>
+          <t>36141; 63195</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>48425; 80815</t>
+          <t>48021; 80630</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>58291; 90426</t>
+          <t>56420; 89752</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>12250; 30475</t>
+          <t>13218; 31847</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>20743; 43260</t>
+          <t>21302; 45371</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18371; 38529</t>
+          <t>18835; 39684</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>52820; 86850</t>
+          <t>53517; 85331</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>76378; 117202</t>
+          <t>76889; 116045</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>82691; 121724</t>
+          <t>81514; 119615</t>
         </is>
       </c>
     </row>
